--- a/docs/video_manual/v1.6/exports/Report_Invoice-wise_with_Recognition_Code.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Invoice-wise_with_Recognition_Code.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
         <v>16.67</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>83.34</v>
+        <v>83.33</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>18450</v>
@@ -688,7 +688,7 @@
         <v>16.67</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>250.01</v>
+        <v>250</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>52300</v>
@@ -889,10 +889,10 @@
         <v>4</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>16.66</v>
+        <v>16.67</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>66.66</v>
+        <v>66.67</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>14200</v>
@@ -1224,15 +1224,19 @@
       <c r="J14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>105</v>
+      </c>
       <c r="M14" s="6" t="n">
         <v>24100</v>
       </c>
       <c r="N14" s="6" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1289,10 +1293,10 @@
         <v>10</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>33500</v>
@@ -1424,15 +1428,19 @@
       <c r="J17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>126</v>
+      </c>
       <c r="M17" s="6" t="n">
         <v>29900</v>
       </c>
       <c r="N17" s="6" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1459,10 +1467,10 @@
         <v>127</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>19.34</v>
+        <v>20.76</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>2456.02</v>
+        <v>2637</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>428700</v>

--- a/docs/video_manual/v1.6/exports/Report_Invoice-wise_with_Recognition_Code.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Invoice-wise_with_Recognition_Code.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,20 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,94 +489,97 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Depot</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Customer Type</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Original ERP Invoice No</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Invoice Recognition Code</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Rate/Box</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Transportation Expense</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Sales Value</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Taxable Amount</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Dispatch Status</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>ERP</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>46311</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -613,19 +622,19 @@
           <t>ABC-RET-C025-GUMA-001245</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>16.67</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <v>83.33</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="7" t="n">
         <v>18450</v>
       </c>
-      <c r="N5" s="6" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -638,7 +647,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>46311</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,19 +690,19 @@
           <t>ABC-STK-C031-GUMA-001246</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>16.67</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="7" t="n">
         <v>52300</v>
       </c>
-      <c r="N6" s="6" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -706,7 +715,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>46311</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -749,19 +758,19 @@
           <t>ABC-HSP-C040-GUMA-001247</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>16.67</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" s="7" t="n">
         <v>21600</v>
       </c>
-      <c r="N7" s="6" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -774,7 +783,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>46311</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -817,19 +826,19 @@
           <t>ABC-CHN-C071-BSP-001248</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="7" t="n">
         <v>264</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="M8" s="7" t="n">
         <v>39900</v>
       </c>
-      <c r="N8" s="6" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -842,7 +851,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>46311</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -885,19 +894,19 @@
           <t>XYZ-RET-C025-GUMA-002601</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="7" t="n">
         <v>16.67</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="7" t="n">
         <v>66.67</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="M9" s="7" t="n">
         <v>14200</v>
       </c>
-      <c r="N9" s="6" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -910,7 +919,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,19 +962,19 @@
           <t>ABC-SST-C080-BSP-001249</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="7" t="n">
         <v>440</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="M10" s="7" t="n">
         <v>68200</v>
       </c>
-      <c r="N10" s="6" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -978,7 +987,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1021,15 +1030,15 @@
           <t>ABC-GOV-C090-BSP-001250</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="6" t="n">
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="n">
         <v>27750</v>
       </c>
-      <c r="N11" s="6" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1042,7 +1051,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1085,19 +1094,19 @@
           <t>PQR-CHN-C071-BSP-000313</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>31200</v>
       </c>
-      <c r="N12" s="6" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -1110,7 +1119,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1153,19 +1162,19 @@
           <t>PQR-STK-C031-KVR-000311</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>19800</v>
       </c>
-      <c r="N13" s="6" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -1178,7 +1187,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1221,19 +1230,19 @@
           <t>PQR-RET-C052-KVR-000312</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>24100</v>
       </c>
-      <c r="N14" s="6" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -1246,7 +1255,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1289,19 +1298,19 @@
           <t>XYZ-RET-C052-GUMA-002602</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>33500</v>
       </c>
-      <c r="N15" s="6" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>Slip Printed</t>
@@ -1314,7 +1323,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1357,19 +1366,19 @@
           <t>XYZ-STK-C031-KVR-002603</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>47800</v>
       </c>
-      <c r="N16" s="6" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -1382,7 +1391,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1425,19 +1434,19 @@
           <t>XYZ-DST-C063-KVR-002604</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>29900</v>
       </c>
-      <c r="N17" s="6" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Dispatched</t>
@@ -1450,36 +1459,36 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="9" t="n">
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="10" t="n">
         <v>127</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K18" s="11" t="n">
         <v>20.76</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="11" t="n">
         <v>2637</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="11" t="n">
         <v>428700</v>
       </c>
-      <c r="N18" s="10" t="n">
+      <c r="N18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:P18"/>
